--- a/artfynd/A 30437-2021 artfynd.xlsx
+++ b/artfynd/A 30437-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856866</v>
       </c>
       <c r="B2" t="n">
-        <v>93208</v>
+        <v>93214</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856867</v>
       </c>
       <c r="B3" t="n">
-        <v>93208</v>
+        <v>93214</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30437-2021 artfynd.xlsx
+++ b/artfynd/A 30437-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856866</v>
       </c>
       <c r="B2" t="n">
-        <v>93214</v>
+        <v>93216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856867</v>
       </c>
       <c r="B3" t="n">
-        <v>93214</v>
+        <v>93216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 30437-2021 artfynd.xlsx
+++ b/artfynd/A 30437-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856866</v>
       </c>
       <c r="B2" t="n">
-        <v>93216</v>
+        <v>93244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856867</v>
       </c>
       <c r="B3" t="n">
-        <v>93216</v>
+        <v>93244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>133856923</v>
       </c>
       <c r="B4" t="n">
-        <v>79000</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30437-2021 artfynd.xlsx
+++ b/artfynd/A 30437-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856866</v>
       </c>
       <c r="B2" t="n">
-        <v>93244</v>
+        <v>93254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856867</v>
       </c>
       <c r="B3" t="n">
-        <v>93244</v>
+        <v>93254</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>133856923</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30437-2021 artfynd.xlsx
+++ b/artfynd/A 30437-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856866</v>
       </c>
       <c r="B2" t="n">
-        <v>93254</v>
+        <v>93256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856867</v>
       </c>
       <c r="B3" t="n">
-        <v>93254</v>
+        <v>93256</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>133856923</v>
       </c>
       <c r="B4" t="n">
-        <v>79024</v>
+        <v>79025</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 30437-2021 artfynd.xlsx
+++ b/artfynd/A 30437-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133856866</v>
       </c>
       <c r="B2" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>133856867</v>
       </c>
       <c r="B3" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>133856923</v>
       </c>
       <c r="B4" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
